--- a/Acciones de juego.xlsx
+++ b/Acciones de juego.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://indeportesantioquia-my.sharepoint.com/personal/anavarro_indeportesantioquia_gov_co/Documents/AI/2025/DEPORTES/FUTBOL/futbol_liga/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{9281E0E7-F489-469C-908D-6508067067EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37A08BB9-FD0E-4276-B60E-4C8A23DF3193}"/>
+  <xr:revisionPtr revIDLastSave="60" documentId="8_{9281E0E7-F489-469C-908D-6508067067EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC723A62-CB68-44D9-9350-2A7DB78FD4D4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{CCF08D88-C03F-4F55-85B1-B30C0A363DE1}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
     <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
+    <sheet name="Hoja3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="97">
   <si>
     <t>OFENSIVA</t>
   </si>
@@ -195,9 +196,6 @@
     <t>Reanudacion</t>
   </si>
   <si>
-    <t>Categori­a</t>
-  </si>
-  <si>
     <t>Acción</t>
   </si>
   <si>
@@ -267,23 +265,77 @@
     <t>OFFSIDE</t>
   </si>
   <si>
-    <t>SUSTITUCIÃ“N</t>
-  </si>
-  <si>
     <t>Entra / Sale (minuto)</t>
   </si>
   <si>
-    <t>REANUDACIÃ“N TIEMPO</t>
-  </si>
-  <si>
-    <t>1Âº / 2Âº tiempo</t>
+    <t>timestamp</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Team</t>
+  </si>
+  <si>
+    <t>Periodo</t>
+  </si>
+  <si>
+    <t>Tiempo</t>
+  </si>
+  <si>
+    <t>Categoria</t>
+  </si>
+  <si>
+    <t>SUSTITUCION</t>
+  </si>
+  <si>
+    <t>ABP</t>
+  </si>
+  <si>
+    <t>Directo/Desviado</t>
+  </si>
+  <si>
+    <t>🏟️ Equipos del Evento</t>
+  </si>
+  <si>
+    <t>Equipos registrados:</t>
+  </si>
+  <si>
+    <t>Antioquia</t>
+  </si>
+  <si>
+    <t>Meta</t>
+  </si>
+  <si>
+    <t>Cundinamarca</t>
+  </si>
+  <si>
+    <t>Cauca</t>
+  </si>
+  <si>
+    <t>➕➖ Gestión rápida de equipos</t>
+  </si>
+  <si>
+    <t>Agregar equipo</t>
+  </si>
+  <si>
+    <t>+</t>
+  </si>
+  <si>
+    <t>Eliminar equipo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siguiente </t>
+  </si>
+  <si>
+    <t>Dorsal</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -299,13 +351,43 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="13.5"/>
+      <color rgb="FF31333F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF31333F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF31333F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <color rgb="FF31333F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -320,9 +402,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -338,6 +432,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>409575</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>144607</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9414550D-B979-631D-6705-FAA6F4CAC79C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2828925" y="1704975"/>
+          <a:ext cx="409575" cy="335107"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -927,192 +1070,285 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDD90CAA-0ECD-405B-A626-BB4DF3F989FB}">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H1" t="s">
         <v>52</v>
       </c>
-      <c r="B1" t="s">
+      <c r="I1" t="s">
         <v>53</v>
       </c>
-      <c r="C1" t="s">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="H2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" t="s">
         <v>55</v>
       </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>54</v>
+      </c>
+      <c r="H3" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H4" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B4" t="s">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>54</v>
+      </c>
+      <c r="H5" t="s">
+        <v>4</v>
+      </c>
+      <c r="I5" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" t="s">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>54</v>
+      </c>
+      <c r="H6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" t="s">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>54</v>
+      </c>
+      <c r="H7" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>55</v>
-      </c>
-      <c r="B7" t="s">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H8" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="I8" t="s">
         <v>62</v>
       </c>
-      <c r="C8" t="s">
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="H9" t="s">
         <v>64</v>
       </c>
-      <c r="B9" t="s">
+      <c r="I9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>63</v>
+      </c>
+      <c r="H10" t="s">
         <v>65</v>
       </c>
-      <c r="C9" t="s">
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>64</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="H11" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>64</v>
-      </c>
-      <c r="B11" t="s">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>63</v>
+      </c>
+      <c r="H12" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>64</v>
-      </c>
-      <c r="B12" t="s">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>63</v>
+      </c>
+      <c r="H13" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>64</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="I13" t="s">
         <v>69</v>
       </c>
-      <c r="C13" t="s">
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>63</v>
+      </c>
+      <c r="H14" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>64</v>
-      </c>
-      <c r="B14" t="s">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>63</v>
+      </c>
+      <c r="H15" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>64</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="I15" t="s">
         <v>72</v>
       </c>
-      <c r="C15" t="s">
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="H16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>73</v>
+      </c>
+      <c r="H17" t="s">
         <v>74</v>
       </c>
-      <c r="B16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>74</v>
-      </c>
-      <c r="B17" t="s">
+    </row>
+    <row r="18" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>73</v>
+      </c>
+      <c r="H18" t="s">
+        <v>82</v>
+      </c>
+      <c r="I18" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>74</v>
-      </c>
-      <c r="B18" t="s">
-        <v>76</v>
-      </c>
-      <c r="C18" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>74</v>
-      </c>
-      <c r="B19" t="s">
-        <v>78</v>
-      </c>
-      <c r="C19" t="s">
-        <v>79</v>
+    <row r="19" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>73</v>
+      </c>
+      <c r="H19" t="s">
+        <v>83</v>
+      </c>
+      <c r="I19" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="20" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>73</v>
+      </c>
+      <c r="H20" t="s">
+        <v>83</v>
+      </c>
+      <c r="I20" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77433FEC-3924-4C7B-A09E-968247866437}">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="31" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="27" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C4" s="6"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C7" s="6"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>95</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>